--- a/00-TrainRnns/tau-6/Theta/Metricas.xlsx
+++ b/00-TrainRnns/tau-6/Theta/Metricas.xlsx
@@ -470,14 +470,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>model_arch31_r0.01_Ld0.7_Lp0.3_seed7789</t>
+          <t>model_arch27_r0.01_Ld0.5_Lp0.5_seed686</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.970951334053008</v>
+        <v>0.9055547888872781</v>
       </c>
       <c r="E2" t="n">
-        <v>0.006905553630622341</v>
+        <v>0.02245185619485863</v>
       </c>
     </row>
     <row r="3">
@@ -493,14 +493,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>model_arch98_r0.9_Ld0.7_Lp0.3_seed2693</t>
+          <t>model_arch20_r0.9_Ld0.5_Lp0.5_seed1257</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9704609046816363</v>
+        <v>0.9026001179453695</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007022140269479362</v>
+        <v>0.02315425122695491</v>
       </c>
     </row>
     <row r="4">
@@ -516,14 +516,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>model_arch87_r0.01_Ld0.7_Lp0.3_seed2693</t>
+          <t>model_arch36_r0.9_Ld0.5_Lp0.5_seed686</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.9703736465383873</v>
+        <v>0.914859345822861</v>
       </c>
       <c r="E4" t="n">
-        <v>0.007042883589982063</v>
+        <v>0.02023994336398731</v>
       </c>
     </row>
     <row r="5">
@@ -539,14 +539,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>model_arch77_r0.01_Ld0.5_Lp0.5_seed686</t>
+          <t>model_arch44_r0.9_Ld0.5_Lp0.5_seed4358</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9754469004282048</v>
+        <v>0.9275204748421462</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005836851379007993</v>
+        <v>0.01723009411216802</v>
       </c>
     </row>
     <row r="6">
@@ -562,14 +562,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>model_arch42_r0.9_Ld0.7_Lp0.3_seed4705</t>
+          <t>model_arch38_r0.01_Ld0.7_Lp0.3_seed2693</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.9708411144328279</v>
+        <v>0.9466691413637521</v>
       </c>
       <c r="E6" t="n">
-        <v>0.006931755436229855</v>
+        <v>0.01267800404850898</v>
       </c>
     </row>
     <row r="7">
@@ -589,10 +589,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.9758801159994713</v>
+        <v>0.9236967811730619</v>
       </c>
       <c r="E7" t="n">
-        <v>0.005733865811049008</v>
+        <v>0.01813907636102984</v>
       </c>
     </row>
     <row r="8">
@@ -608,14 +608,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>model_arch31_r0.01_Ld0.7_Lp0.3_seed7789</t>
+          <t>model_arch27_r0.01_Ld0.5_Lp0.5_seed686</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.8705628351956267</v>
+        <v>0.963866111109712</v>
       </c>
       <c r="E8" t="n">
-        <v>0.132264382107111</v>
+        <v>0.03692313945862533</v>
       </c>
     </row>
     <row r="9">
@@ -631,14 +631,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>model_arch98_r0.9_Ld0.7_Lp0.3_seed2693</t>
+          <t>model_arch20_r0.9_Ld0.5_Lp0.5_seed1257</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.8410446724071261</v>
+        <v>0.9532768879763971</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1624272921805727</v>
+        <v>0.04774365655538805</v>
       </c>
     </row>
     <row r="10">
@@ -654,14 +654,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>model_arch87_r0.01_Ld0.7_Lp0.3_seed2693</t>
+          <t>model_arch36_r0.9_Ld0.5_Lp0.5_seed686</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.8398461257257787</v>
+        <v>0.9347067576046504</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1636520179884543</v>
+        <v>0.06671940299559889</v>
       </c>
     </row>
     <row r="11">
@@ -677,14 +677,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>model_arch77_r0.01_Ld0.5_Lp0.5_seed686</t>
+          <t>model_arch44_r0.9_Ld0.5_Lp0.5_seed4358</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.7506656506837367</v>
+        <v>0.9282770356469973</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2547804079318021</v>
+        <v>0.07328956546118462</v>
       </c>
     </row>
     <row r="12">
@@ -700,14 +700,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>model_arch42_r0.9_Ld0.7_Lp0.3_seed4705</t>
+          <t>model_arch38_r0.01_Ld0.7_Lp0.3_seed2693</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.5810758896020003</v>
+        <v>0.902089662137139</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4280744150669968</v>
+        <v>0.1000489338506604</v>
       </c>
     </row>
     <row r="13">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.8712615380127817</v>
+        <v>0.9448220914691261</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1315504179490797</v>
+        <v>0.05638312604288546</v>
       </c>
     </row>
     <row r="14">
@@ -746,14 +746,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>model_arch31_r0.01_Ld0.7_Lp0.3_seed7789</t>
+          <t>model_arch27_r0.01_Ld0.5_Lp0.5_seed686</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.8991752260908904</v>
+        <v>0.916343817608014</v>
       </c>
       <c r="E14" t="n">
-        <v>0.02101552891274211</v>
+        <v>0.01743697358918218</v>
       </c>
     </row>
     <row r="15">
@@ -769,14 +769,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>model_arch98_r0.9_Ld0.7_Lp0.3_seed2693</t>
+          <t>model_arch20_r0.9_Ld0.5_Lp0.5_seed1257</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.9047613183985981</v>
+        <v>0.9153510019530957</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0198511852712904</v>
+        <v>0.01764391227391227</v>
       </c>
     </row>
     <row r="16">
@@ -792,14 +792,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>model_arch87_r0.01_Ld0.7_Lp0.3_seed2693</t>
+          <t>model_arch36_r0.9_Ld0.5_Lp0.5_seed686</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.9170631499826242</v>
+        <v>0.8531529142432377</v>
       </c>
       <c r="E16" t="n">
-        <v>0.01728703870978321</v>
+        <v>0.03060824296273805</v>
       </c>
     </row>
     <row r="17">
@@ -815,14 +815,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>model_arch77_r0.01_Ld0.5_Lp0.5_seed686</t>
+          <t>model_arch44_r0.9_Ld0.5_Lp0.5_seed4358</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.2943482415145049</v>
+        <v>0.9337180536768359</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1470833442795289</v>
+        <v>0.01381555450452066</v>
       </c>
     </row>
     <row r="18">
@@ -838,14 +838,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>model_arch42_r0.9_Ld0.7_Lp0.3_seed4705</t>
+          <t>model_arch38_r0.01_Ld0.7_Lp0.3_seed2693</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.8630557078314577</v>
+        <v>0.9238035806407467</v>
       </c>
       <c r="E18" t="n">
-        <v>0.02854414267367852</v>
+        <v>0.01588208921286883</v>
       </c>
     </row>
     <row r="19">
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.8721335848122628</v>
+        <v>0.9181510244471375</v>
       </c>
       <c r="E19" t="n">
-        <v>0.02665198483627633</v>
+        <v>0.01706028633161252</v>
       </c>
     </row>
     <row r="20">
@@ -884,14 +884,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>model_arch31_r0.01_Ld0.7_Lp0.3_seed7789</t>
+          <t>model_arch27_r0.01_Ld0.5_Lp0.5_seed686</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-13.7302041212995</v>
+        <v>-7.173512891350642</v>
       </c>
       <c r="E20" t="n">
-        <v>10.21900009587438</v>
+        <v>5.670330725394867</v>
       </c>
     </row>
     <row r="21">
@@ -907,14 +907,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>model_arch98_r0.9_Ld0.7_Lp0.3_seed2693</t>
+          <t>model_arch20_r0.9_Ld0.5_Lp0.5_seed1257</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-20.036679907714</v>
+        <v>-12.03443494474302</v>
       </c>
       <c r="E21" t="n">
-        <v>14.59408384456541</v>
+        <v>9.042569325797396</v>
       </c>
     </row>
     <row r="22">
@@ -930,14 +930,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>model_arch87_r0.01_Ld0.7_Lp0.3_seed2693</t>
+          <t>model_arch36_r0.9_Ld0.5_Lp0.5_seed686</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-17.47828540827605</v>
+        <v>-6.920350564607268</v>
       </c>
       <c r="E22" t="n">
-        <v>12.81921138388872</v>
+        <v>5.494700719187316</v>
       </c>
     </row>
     <row r="23">
@@ -953,14 +953,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>model_arch77_r0.01_Ld0.5_Lp0.5_seed686</t>
+          <t>model_arch44_r0.9_Ld0.5_Lp0.5_seed4358</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-27.27760706235</v>
+        <v>-10.20749571881077</v>
       </c>
       <c r="E23" t="n">
-        <v>19.61743821753365</v>
+        <v>7.775140037566236</v>
       </c>
     </row>
     <row r="24">
@@ -976,14 +976,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>model_arch42_r0.9_Ld0.7_Lp0.3_seed4705</t>
+          <t>model_arch38_r0.01_Ld0.7_Lp0.3_seed2693</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-18.57111014867603</v>
+        <v>-12.08654123623143</v>
       </c>
       <c r="E24" t="n">
-        <v>13.577352685595</v>
+        <v>9.078717786017698</v>
       </c>
     </row>
     <row r="25">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-19.18228640394582</v>
+        <v>-9.55495156470394</v>
       </c>
       <c r="E25" t="n">
-        <v>14.0013529343198</v>
+        <v>7.322441030921942</v>
       </c>
     </row>
     <row r="26">
@@ -1022,14 +1022,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>model_arch31_r0.01_Ld0.7_Lp0.3_seed7789</t>
+          <t>model_arch27_r0.01_Ld0.5_Lp0.5_seed686</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-18.05334767073649</v>
+        <v>-20.51413376573982</v>
       </c>
       <c r="E26" t="n">
-        <v>22.15022801099698</v>
+        <v>25.01098371821217</v>
       </c>
     </row>
     <row r="27">
@@ -1045,14 +1045,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>model_arch98_r0.9_Ld0.7_Lp0.3_seed2693</t>
+          <t>model_arch20_r0.9_Ld0.5_Lp0.5_seed1257</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-18.93898263235175</v>
+        <v>-15.38407001550079</v>
       </c>
       <c r="E27" t="n">
-        <v>23.17981171845316</v>
+        <v>19.04709308112117</v>
       </c>
     </row>
     <row r="28">
@@ -1068,14 +1068,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>model_arch87_r0.01_Ld0.7_Lp0.3_seed2693</t>
+          <t>model_arch36_r0.9_Ld0.5_Lp0.5_seed686</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-20.34441572812247</v>
+        <v>-17.47763755378091</v>
       </c>
       <c r="E28" t="n">
-        <v>24.81368016317458</v>
+        <v>21.48094350629078</v>
       </c>
     </row>
     <row r="29">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>model_arch77_r0.01_Ld0.5_Lp0.5_seed686</t>
+          <t>model_arch44_r0.9_Ld0.5_Lp0.5_seed4358</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-15.30069060050563</v>
+        <v>-18.34375045008194</v>
       </c>
       <c r="E29" t="n">
-        <v>18.9501613982756</v>
+        <v>22.48783208397615</v>
       </c>
     </row>
     <row r="30">
@@ -1114,14 +1114,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>model_arch42_r0.9_Ld0.7_Lp0.3_seed4705</t>
+          <t>model_arch38_r0.01_Ld0.7_Lp0.3_seed2693</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-10.58112438936931</v>
+        <v>-20.43243114177769</v>
       </c>
       <c r="E30" t="n">
-        <v>13.46348947603771</v>
+        <v>24.91600136754433</v>
       </c>
     </row>
     <row r="31">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-16.43058882610826</v>
+        <v>-18.3691832066115</v>
       </c>
       <c r="E31" t="n">
-        <v>20.26371026951979</v>
+        <v>22.51739861295642</v>
       </c>
     </row>
     <row r="32">
@@ -1160,14 +1160,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>model_arch31_r0.01_Ld0.7_Lp0.3_seed7789</t>
+          <t>model_arch27_r0.01_Ld0.5_Lp0.5_seed686</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.7931390056050667</v>
+        <v>0.7866843754160708</v>
       </c>
       <c r="E32" t="n">
-        <v>0.06176371254107262</v>
+        <v>0.0636909097138318</v>
       </c>
     </row>
     <row r="33">
@@ -1183,14 +1183,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>model_arch98_r0.9_Ld0.7_Lp0.3_seed2693</t>
+          <t>model_arch20_r0.9_Ld0.5_Lp0.5_seed1257</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.4193415501677461</v>
+        <v>0.8324307403547023</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1733706331872036</v>
+        <v>0.05003214653262839</v>
       </c>
     </row>
     <row r="34">
@@ -1206,14 +1206,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>model_arch87_r0.01_Ld0.7_Lp0.3_seed2693</t>
+          <t>model_arch36_r0.9_Ld0.5_Lp0.5_seed686</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.6763670750533493</v>
+        <v>0.8782139992638546</v>
       </c>
       <c r="E34" t="n">
-        <v>0.09662899960284177</v>
+        <v>0.03636236770008672</v>
       </c>
     </row>
     <row r="35">
@@ -1229,14 +1229,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>model_arch77_r0.01_Ld0.5_Lp0.5_seed686</t>
+          <t>model_arch44_r0.9_Ld0.5_Lp0.5_seed4358</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-1.471621695173377</v>
+        <v>0.8195569006586486</v>
       </c>
       <c r="E35" t="n">
-        <v>0.737966731415394</v>
+        <v>0.05387596511530841</v>
       </c>
     </row>
     <row r="36">
@@ -1252,14 +1252,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>model_arch42_r0.9_Ld0.7_Lp0.3_seed4705</t>
+          <t>model_arch38_r0.01_Ld0.7_Lp0.3_seed2693</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.6988624130937502</v>
+        <v>0.8128187640583093</v>
       </c>
       <c r="E36" t="n">
-        <v>0.08991243326173164</v>
+        <v>0.05588781047679446</v>
       </c>
     </row>
     <row r="37">
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.4680662644674529</v>
+        <v>0.8313781523289268</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1588226065935217</v>
+        <v>0.0503464239750159</v>
       </c>
     </row>
     <row r="38">
@@ -1298,14 +1298,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>model_arch31_r0.01_Ld0.7_Lp0.3_seed7789</t>
+          <t>model_arch27_r0.01_Ld0.5_Lp0.5_seed686</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-2.738174242228233</v>
+        <v>-4.182040983825009</v>
       </c>
       <c r="E38" t="n">
-        <v>0.7701830985485668</v>
+        <v>1.06766569001583</v>
       </c>
     </row>
     <row r="39">
@@ -1321,14 +1321,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>model_arch98_r0.9_Ld0.7_Lp0.3_seed2693</t>
+          <t>model_arch20_r0.9_Ld0.5_Lp0.5_seed1257</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-3.438623551977228</v>
+        <v>-2.081648278490756</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9144979926122311</v>
+        <v>0.6349178144114873</v>
       </c>
     </row>
     <row r="40">
@@ -1344,14 +1344,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>model_arch87_r0.01_Ld0.7_Lp0.3_seed2693</t>
+          <t>model_arch36_r0.9_Ld0.5_Lp0.5_seed686</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-3.344140479721651</v>
+        <v>-3.600851569033428</v>
       </c>
       <c r="E40" t="n">
-        <v>0.8950314668071599</v>
+        <v>0.9479221373287323</v>
       </c>
     </row>
     <row r="41">
@@ -1367,14 +1367,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>model_arch77_r0.01_Ld0.5_Lp0.5_seed686</t>
+          <t>model_arch44_r0.9_Ld0.5_Lp0.5_seed4358</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-3.726273427940691</v>
+        <v>-3.226613279612999</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9737630397745578</v>
+        <v>0.8708171158224225</v>
       </c>
     </row>
     <row r="42">
@@ -1390,14 +1390,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>model_arch42_r0.9_Ld0.7_Lp0.3_seed4705</t>
+          <t>model_arch38_r0.01_Ld0.7_Lp0.3_seed2693</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>-3.560675433738309</v>
+        <v>-3.833075059255643</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9396445723025347</v>
+        <v>0.9957675815658361</v>
       </c>
     </row>
     <row r="43">
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>-3.329912355997344</v>
+        <v>-3.308550898707379</v>
       </c>
       <c r="E43" t="n">
-        <v>0.892100019606885</v>
+        <v>0.8876988782210059</v>
       </c>
     </row>
     <row r="44">
@@ -1436,14 +1436,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>model_arch31_r0.01_Ld0.7_Lp0.3_seed7789</t>
+          <t>model_arch27_r0.01_Ld0.5_Lp0.5_seed686</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-4.649695642891582</v>
+        <v>-4.495401798367133</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9693933859539161</v>
+        <v>0.9429191399361517</v>
       </c>
     </row>
     <row r="45">
@@ -1459,14 +1459,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>model_arch98_r0.9_Ld0.7_Lp0.3_seed2693</t>
+          <t>model_arch20_r0.9_Ld0.5_Lp0.5_seed1257</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>-4.019647473103438</v>
+        <v>-2.477156163963692</v>
       </c>
       <c r="E45" t="n">
-        <v>0.8612876458874653</v>
+        <v>0.596621906795339</v>
       </c>
     </row>
     <row r="46">
@@ -1482,14 +1482,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>model_arch87_r0.01_Ld0.7_Lp0.3_seed2693</t>
+          <t>model_arch36_r0.9_Ld0.5_Lp0.5_seed686</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>-4.982436934538161</v>
+        <v>-4.09367050895371</v>
       </c>
       <c r="E46" t="n">
-        <v>1.026486232674216</v>
+        <v>0.8739887621771133</v>
       </c>
     </row>
     <row r="47">
@@ -1505,14 +1505,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>model_arch77_r0.01_Ld0.5_Lp0.5_seed686</t>
+          <t>model_arch44_r0.9_Ld0.5_Lp0.5_seed4358</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-3.418757106405363</v>
+        <v>-4.369044789852688</v>
       </c>
       <c r="E47" t="n">
-        <v>0.7581848977078471</v>
+        <v>0.9212383882523082</v>
       </c>
     </row>
     <row r="48">
@@ -1528,14 +1528,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>model_arch42_r0.9_Ld0.7_Lp0.3_seed4705</t>
+          <t>model_arch38_r0.01_Ld0.7_Lp0.3_seed2693</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-2.147538227161453</v>
+        <v>-4.599268988647823</v>
       </c>
       <c r="E48" t="n">
-        <v>0.5400649755861512</v>
+        <v>0.9607410145361407</v>
       </c>
     </row>
     <row r="49">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-3.772167674309421</v>
+        <v>-3.963202999691415</v>
       </c>
       <c r="E49" t="n">
-        <v>0.8188242469236693</v>
+        <v>0.85160271723682</v>
       </c>
     </row>
     <row r="50">
@@ -1574,14 +1574,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>model_arch31_r0.01_Ld0.7_Lp0.3_seed7789</t>
+          <t>model_arch27_r0.01_Ld0.5_Lp0.5_seed686</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>-17.82438951680118</v>
+        <v>-18.23998486184094</v>
       </c>
       <c r="E50" t="n">
-        <v>17.91982810137929</v>
+        <v>18.31545299727293</v>
       </c>
     </row>
     <row r="51">
@@ -1597,14 +1597,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>model_arch98_r0.9_Ld0.7_Lp0.3_seed2693</t>
+          <t>model_arch20_r0.9_Ld0.5_Lp0.5_seed1257</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>-18.25194314221064</v>
+        <v>-10.74339898764885</v>
       </c>
       <c r="E51" t="n">
-        <v>18.32683665082631</v>
+        <v>11.17909778677055</v>
       </c>
     </row>
     <row r="52">
@@ -1620,14 +1620,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>model_arch87_r0.01_Ld0.7_Lp0.3_seed2693</t>
+          <t>model_arch36_r0.9_Ld0.5_Lp0.5_seed686</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>-19.11576929008306</v>
+        <v>-14.44537153081915</v>
       </c>
       <c r="E52" t="n">
-        <v>19.14915368084392</v>
+        <v>14.70318081482461</v>
       </c>
     </row>
     <row r="53">
@@ -1643,14 +1643,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>model_arch77_r0.01_Ld0.5_Lp0.5_seed686</t>
+          <t>model_arch44_r0.9_Ld0.5_Lp0.5_seed4358</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>-15.75419614038955</v>
+        <v>-16.17732934256273</v>
       </c>
       <c r="E53" t="n">
-        <v>15.94911296032252</v>
+        <v>16.35191349949337</v>
       </c>
     </row>
     <row r="54">
@@ -1666,14 +1666,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>model_arch42_r0.9_Ld0.7_Lp0.3_seed4705</t>
+          <t>model_arch38_r0.01_Ld0.7_Lp0.3_seed2693</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>-9.028977577572958</v>
+        <v>-18.56977562861328</v>
       </c>
       <c r="E54" t="n">
-        <v>9.54705883355701</v>
+        <v>18.62939645050991</v>
       </c>
     </row>
     <row r="55">
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>-15.74050830764244</v>
+        <v>-15.49773841326213</v>
       </c>
       <c r="E55" t="n">
-        <v>15.93608286393136</v>
+        <v>15.70497870134472</v>
       </c>
     </row>
     <row r="56">
@@ -1712,14 +1712,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>model_arch31_r0.01_Ld0.7_Lp0.3_seed7789</t>
+          <t>model_arch27_r0.01_Ld0.5_Lp0.5_seed686</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>-36.82154376777819</v>
+        <v>-32.6536493656232</v>
       </c>
       <c r="E56" t="n">
-        <v>23.61286466113269</v>
+        <v>21.0107517742488</v>
       </c>
     </row>
     <row r="57">
@@ -1735,14 +1735,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>model_arch98_r0.9_Ld0.7_Lp0.3_seed2693</t>
+          <t>model_arch20_r0.9_Ld0.5_Lp0.5_seed1257</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>-23.92881652743528</v>
+        <v>-32.0722955797687</v>
       </c>
       <c r="E57" t="n">
-        <v>15.56363681077517</v>
+        <v>20.64779915788008</v>
       </c>
     </row>
     <row r="58">
@@ -1758,14 +1758,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>model_arch87_r0.01_Ld0.7_Lp0.3_seed2693</t>
+          <t>model_arch36_r0.9_Ld0.5_Lp0.5_seed686</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>-28.3880477178117</v>
+        <v>-34.92070394424444</v>
       </c>
       <c r="E58" t="n">
-        <v>18.34763799374025</v>
+        <v>22.42612638912613</v>
       </c>
     </row>
     <row r="59">
@@ -1781,14 +1781,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>model_arch77_r0.01_Ld0.5_Lp0.5_seed686</t>
+          <t>model_arch44_r0.9_Ld0.5_Lp0.5_seed4358</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>-12.17731405511332</v>
+        <v>-36.34310322262429</v>
       </c>
       <c r="E59" t="n">
-        <v>8.226901981873043</v>
+        <v>23.31416316151959</v>
       </c>
     </row>
     <row r="60">
@@ -1804,14 +1804,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>model_arch42_r0.9_Ld0.7_Lp0.3_seed4705</t>
+          <t>model_arch38_r0.01_Ld0.7_Lp0.3_seed2693</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>-26.64507675460181</v>
+        <v>-35.44890294160106</v>
       </c>
       <c r="E60" t="n">
-        <v>17.25946090305201</v>
+        <v>22.75589324146052</v>
       </c>
     </row>
     <row r="61">
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>-24.86204101374408</v>
+        <v>-34.26357577683979</v>
       </c>
       <c r="E61" t="n">
-        <v>16.14627044490087</v>
+        <v>22.01586607354473</v>
       </c>
     </row>
   </sheetData>
@@ -1869,27 +1869,27 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>model_arch31_r0.01_Ld0.7_Lp0.3_seed7789</t>
+          <t>model_arch20_r0.9_Ld0.5_Lp0.5_seed1257</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>model_arch42_r0.9_Ld0.7_Lp0.3_seed4705</t>
+          <t>model_arch27_r0.01_Ld0.5_Lp0.5_seed686</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>model_arch77_r0.01_Ld0.5_Lp0.5_seed686</t>
+          <t>model_arch36_r0.9_Ld0.5_Lp0.5_seed686</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>model_arch87_r0.01_Ld0.7_Lp0.3_seed2693</t>
+          <t>model_arch38_r0.01_Ld0.7_Lp0.3_seed2693</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>model_arch98_r0.9_Ld0.7_Lp0.3_seed2693</t>
+          <t>model_arch44_r0.9_Ld0.5_Lp0.5_seed4358</t>
         </is>
       </c>
     </row>
@@ -1905,22 +1905,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4680662644674529</v>
+        <v>0.8313781523289268</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7931390056050667</v>
+        <v>0.8324307403547023</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6988624130937502</v>
+        <v>0.7866843754160708</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.471621695173377</v>
+        <v>0.8782139992638546</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6763670750533493</v>
+        <v>0.8128187640583093</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4193415501677461</v>
+        <v>0.8195569006586486</v>
       </c>
     </row>
     <row r="3">
@@ -1935,22 +1935,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-3.329912355997344</v>
+        <v>-3.308550898707379</v>
       </c>
       <c r="D3" t="n">
-        <v>-2.738174242228233</v>
+        <v>-2.081648278490756</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.560675433738309</v>
+        <v>-4.182040983825009</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.726273427940691</v>
+        <v>-3.600851569033428</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.344140479721651</v>
+        <v>-3.833075059255643</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.438623551977228</v>
+        <v>-3.226613279612999</v>
       </c>
     </row>
     <row r="4">
@@ -1965,22 +1965,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9758801159994713</v>
+        <v>0.9236967811730619</v>
       </c>
       <c r="D4" t="n">
-        <v>0.970951334053008</v>
+        <v>0.9026001179453695</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9708411144328279</v>
+        <v>0.9055547888872781</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9754469004282048</v>
+        <v>0.914859345822861</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9703736465383873</v>
+        <v>0.9466691413637521</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9704609046816363</v>
+        <v>0.9275204748421462</v>
       </c>
     </row>
     <row r="5">
@@ -1995,22 +1995,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-3.772167674309421</v>
+        <v>-3.963202999691415</v>
       </c>
       <c r="D5" t="n">
-        <v>-4.649695642891582</v>
+        <v>-2.477156163963692</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.147538227161453</v>
+        <v>-4.495401798367133</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.418757106405363</v>
+        <v>-4.09367050895371</v>
       </c>
       <c r="G5" t="n">
-        <v>-4.982436934538161</v>
+        <v>-4.599268988647823</v>
       </c>
       <c r="H5" t="n">
-        <v>-4.019647473103438</v>
+        <v>-4.369044789852688</v>
       </c>
     </row>
     <row r="6">
@@ -2025,22 +2025,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8712615380127817</v>
+        <v>0.9448220914691261</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8705628351956267</v>
+        <v>0.9532768879763971</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5810758896020003</v>
+        <v>0.963866111109712</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7506656506837367</v>
+        <v>0.9347067576046504</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8398461257257787</v>
+        <v>0.902089662137139</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8410446724071261</v>
+        <v>0.9282770356469973</v>
       </c>
     </row>
     <row r="7">
@@ -2055,22 +2055,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.8721335848122628</v>
+        <v>0.9181510244471375</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8991752260908904</v>
+        <v>0.9153510019530957</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8630557078314577</v>
+        <v>0.916343817608014</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2943482415145049</v>
+        <v>0.8531529142432377</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9170631499826242</v>
+        <v>0.9238035806407467</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9047613183985981</v>
+        <v>0.9337180536768359</v>
       </c>
     </row>
     <row r="8">
@@ -2085,22 +2085,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-19.18228640394582</v>
+        <v>-9.55495156470394</v>
       </c>
       <c r="D8" t="n">
-        <v>-13.7302041212995</v>
+        <v>-12.03443494474302</v>
       </c>
       <c r="E8" t="n">
-        <v>-18.57111014867603</v>
+        <v>-7.173512891350642</v>
       </c>
       <c r="F8" t="n">
-        <v>-27.27760706235</v>
+        <v>-6.920350564607268</v>
       </c>
       <c r="G8" t="n">
-        <v>-17.47828540827605</v>
+        <v>-12.08654123623143</v>
       </c>
       <c r="H8" t="n">
-        <v>-20.036679907714</v>
+        <v>-10.20749571881077</v>
       </c>
     </row>
     <row r="9">
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-16.43058882610826</v>
+        <v>-18.3691832066115</v>
       </c>
       <c r="D9" t="n">
-        <v>-18.05334767073649</v>
+        <v>-15.38407001550079</v>
       </c>
       <c r="E9" t="n">
-        <v>-10.58112438936931</v>
+        <v>-20.51413376573982</v>
       </c>
       <c r="F9" t="n">
-        <v>-15.30069060050563</v>
+        <v>-17.47763755378091</v>
       </c>
       <c r="G9" t="n">
-        <v>-20.34441572812247</v>
+        <v>-20.43243114177769</v>
       </c>
       <c r="H9" t="n">
-        <v>-18.93898263235175</v>
+        <v>-18.34375045008194</v>
       </c>
     </row>
     <row r="10">
@@ -2145,22 +2145,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-24.86204101374408</v>
+        <v>-34.26357577683979</v>
       </c>
       <c r="D10" t="n">
-        <v>-36.82154376777819</v>
+        <v>-32.0722955797687</v>
       </c>
       <c r="E10" t="n">
-        <v>-26.64507675460181</v>
+        <v>-32.6536493656232</v>
       </c>
       <c r="F10" t="n">
-        <v>-12.17731405511332</v>
+        <v>-34.92070394424444</v>
       </c>
       <c r="G10" t="n">
-        <v>-28.3880477178117</v>
+        <v>-35.44890294160106</v>
       </c>
       <c r="H10" t="n">
-        <v>-23.92881652743528</v>
+        <v>-36.34310322262429</v>
       </c>
     </row>
     <row r="11">
@@ -2175,22 +2175,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-15.74050830764244</v>
+        <v>-15.49773841326213</v>
       </c>
       <c r="D11" t="n">
-        <v>-17.82438951680118</v>
+        <v>-10.74339898764885</v>
       </c>
       <c r="E11" t="n">
-        <v>-9.028977577572958</v>
+        <v>-18.23998486184094</v>
       </c>
       <c r="F11" t="n">
-        <v>-15.75419614038955</v>
+        <v>-14.44537153081915</v>
       </c>
       <c r="G11" t="n">
-        <v>-19.11576929008306</v>
+        <v>-18.56977562861328</v>
       </c>
       <c r="H11" t="n">
-        <v>-18.25194314221064</v>
+        <v>-16.17732934256273</v>
       </c>
     </row>
   </sheetData>
@@ -2225,27 +2225,27 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>model_arch31_r0.01_Ld0.7_Lp0.3_seed7789</t>
+          <t>model_arch20_r0.9_Ld0.5_Lp0.5_seed1257</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>model_arch42_r0.9_Ld0.7_Lp0.3_seed4705</t>
+          <t>model_arch27_r0.01_Ld0.5_Lp0.5_seed686</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>model_arch77_r0.01_Ld0.5_Lp0.5_seed686</t>
+          <t>model_arch36_r0.9_Ld0.5_Lp0.5_seed686</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>model_arch87_r0.01_Ld0.7_Lp0.3_seed2693</t>
+          <t>model_arch38_r0.01_Ld0.7_Lp0.3_seed2693</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>model_arch98_r0.9_Ld0.7_Lp0.3_seed2693</t>
+          <t>model_arch44_r0.9_Ld0.5_Lp0.5_seed4358</t>
         </is>
       </c>
     </row>
@@ -2261,22 +2261,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1588226065935217</v>
+        <v>0.0503464239750159</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06176371254107262</v>
+        <v>0.05003214653262839</v>
       </c>
       <c r="E2" t="n">
-        <v>0.08991243326173164</v>
+        <v>0.0636909097138318</v>
       </c>
       <c r="F2" t="n">
-        <v>0.737966731415394</v>
+        <v>0.03636236770008672</v>
       </c>
       <c r="G2" t="n">
-        <v>0.09662899960284177</v>
+        <v>0.05588781047679446</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1733706331872036</v>
+        <v>0.05387596511530841</v>
       </c>
     </row>
     <row r="3">
@@ -2291,22 +2291,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.892100019606885</v>
+        <v>0.8876988782210059</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7701830985485668</v>
+        <v>0.6349178144114873</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9396445723025347</v>
+        <v>1.06766569001583</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9737630397745578</v>
+        <v>0.9479221373287323</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8950314668071599</v>
+        <v>0.9957675815658361</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9144979926122311</v>
+        <v>0.8708171158224225</v>
       </c>
     </row>
     <row r="4">
@@ -2321,22 +2321,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.005733865811049008</v>
+        <v>0.01813907636102984</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006905553630622341</v>
+        <v>0.02315425122695491</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006931755436229855</v>
+        <v>0.02245185619485863</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005836851379007993</v>
+        <v>0.02023994336398731</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007042883589982063</v>
+        <v>0.01267800404850898</v>
       </c>
       <c r="H4" t="n">
-        <v>0.007022140269479362</v>
+        <v>0.01723009411216802</v>
       </c>
     </row>
     <row r="5">
@@ -2351,22 +2351,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8188242469236693</v>
+        <v>0.85160271723682</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9693933859539161</v>
+        <v>0.596621906795339</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5400649755861512</v>
+        <v>0.9429191399361517</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7581848977078471</v>
+        <v>0.8739887621771133</v>
       </c>
       <c r="G5" t="n">
-        <v>1.026486232674216</v>
+        <v>0.9607410145361407</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8612876458874653</v>
+        <v>0.9212383882523082</v>
       </c>
     </row>
     <row r="6">
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.1315504179490797</v>
+        <v>0.05638312604288546</v>
       </c>
       <c r="D6" t="n">
-        <v>0.132264382107111</v>
+        <v>0.04774365655538805</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4280744150669968</v>
+        <v>0.03692313945862533</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2547804079318021</v>
+        <v>0.06671940299559889</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1636520179884543</v>
+        <v>0.1000489338506604</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1624272921805727</v>
+        <v>0.07328956546118462</v>
       </c>
     </row>
     <row r="7">
@@ -2411,22 +2411,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.02665198483627633</v>
+        <v>0.01706028633161252</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02101552891274211</v>
+        <v>0.01764391227391227</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02854414267367852</v>
+        <v>0.01743697358918218</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1470833442795289</v>
+        <v>0.03060824296273805</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01728703870978321</v>
+        <v>0.01588208921286883</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0198511852712904</v>
+        <v>0.01381555450452066</v>
       </c>
     </row>
     <row r="8">
@@ -2441,22 +2441,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14.0013529343198</v>
+        <v>7.322441030921942</v>
       </c>
       <c r="D8" t="n">
-        <v>10.21900009587438</v>
+        <v>9.042569325797396</v>
       </c>
       <c r="E8" t="n">
-        <v>13.577352685595</v>
+        <v>5.670330725394867</v>
       </c>
       <c r="F8" t="n">
-        <v>19.61743821753365</v>
+        <v>5.494700719187316</v>
       </c>
       <c r="G8" t="n">
-        <v>12.81921138388872</v>
+        <v>9.078717786017698</v>
       </c>
       <c r="H8" t="n">
-        <v>14.59408384456541</v>
+        <v>7.775140037566236</v>
       </c>
     </row>
     <row r="9">
@@ -2471,22 +2471,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20.26371026951979</v>
+        <v>22.51739861295642</v>
       </c>
       <c r="D9" t="n">
-        <v>22.15022801099698</v>
+        <v>19.04709308112117</v>
       </c>
       <c r="E9" t="n">
-        <v>13.46348947603771</v>
+        <v>25.01098371821217</v>
       </c>
       <c r="F9" t="n">
-        <v>18.9501613982756</v>
+        <v>21.48094350629078</v>
       </c>
       <c r="G9" t="n">
-        <v>24.81368016317458</v>
+        <v>24.91600136754433</v>
       </c>
       <c r="H9" t="n">
-        <v>23.17981171845316</v>
+        <v>22.48783208397615</v>
       </c>
     </row>
     <row r="10">
@@ -2501,22 +2501,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.14627044490087</v>
+        <v>22.01586607354473</v>
       </c>
       <c r="D10" t="n">
-        <v>23.61286466113269</v>
+        <v>20.64779915788008</v>
       </c>
       <c r="E10" t="n">
-        <v>17.25946090305201</v>
+        <v>21.0107517742488</v>
       </c>
       <c r="F10" t="n">
-        <v>8.226901981873043</v>
+        <v>22.42612638912613</v>
       </c>
       <c r="G10" t="n">
-        <v>18.34763799374025</v>
+        <v>22.75589324146052</v>
       </c>
       <c r="H10" t="n">
-        <v>15.56363681077517</v>
+        <v>23.31416316151959</v>
       </c>
     </row>
     <row r="11">
@@ -2531,22 +2531,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>15.93608286393136</v>
+        <v>15.70497870134472</v>
       </c>
       <c r="D11" t="n">
-        <v>17.91982810137929</v>
+        <v>11.17909778677055</v>
       </c>
       <c r="E11" t="n">
-        <v>9.54705883355701</v>
+        <v>18.31545299727293</v>
       </c>
       <c r="F11" t="n">
-        <v>15.94911296032252</v>
+        <v>14.70318081482461</v>
       </c>
       <c r="G11" t="n">
-        <v>19.14915368084392</v>
+        <v>18.62939645050991</v>
       </c>
       <c r="H11" t="n">
-        <v>18.32683665082631</v>
+        <v>16.35191349949337</v>
       </c>
     </row>
   </sheetData>
